--- a/reports/集团总公司_利润表_2025-11.xlsx
+++ b/reports/集团总公司_利润表_2025-11.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>212764516</v>
+        <v>231269072</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>161915669</v>
+        <v>175253330</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1856491702</v>
+        <v>2013631662</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>656744</v>
+        <v>857250</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>7567667</v>
+        <v>9797842</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>571263</v>
+        <v>749802</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>6565607</v>
+        <v>8575580</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>482360</v>
+        <v>632314</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>5560937</v>
+        <v>7240354</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>446174</v>
+        <v>582787</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5117243</v>
+        <v>6683612</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>241683</v>
+        <v>319934</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>2779945</v>
+        <v>3675520</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>194480</v>
+        <v>251662</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2225057</v>
+        <v>2895205</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>210171812</v>
+        <v>227875323</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>159322965</v>
+        <v>171859581</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>82424196</v>
+        <v>89290209</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>940760713</v>
+        <v>1029445659</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1509551</v>
+        <v>2661709</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>17261062</v>
+        <v>30586041</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1363887</v>
+        <v>1937276</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>15593568</v>
+        <v>22241846</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>72397551</v>
+        <v>76720934</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>834448172</v>
+        <v>878461970</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1558974</v>
+        <v>1945513</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>17819649</v>
+        <v>22249274</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>676065</v>
+        <v>973639</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>7791456</v>
+        <v>11129104</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2433260</v>
+        <v>2924700</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>27837924</v>
+        <v>33400969</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1061736</v>
+        <v>1461059</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>12240220</v>
+        <v>16702840</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>50678906</v>
+        <v>50706061</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>582067638</v>
+        <v>582653504</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>169941</v>
+        <v>170125</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1869556</v>
+        <v>1871580</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3085897</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>35421452</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2053659</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>23609977</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>153919744</v>
+        <v>173599719</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>123509294</v>
+        <v>129767535</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>97125286</v>
+        <v>103493486</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1114318843</v>
+        <v>1192984543</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>26384008</v>
+        <v>26274049</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>301726787</v>
+        <v>301308932</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5126973</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>58941266</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1643186</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>18860815</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1028800</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>11789490</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1236605</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>14150918</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>928622</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>10616687</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>619480</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>7080281</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>516190</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>5902074</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>2845259</v>
+        <v>2868538</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>32815924</v>
+        <v>32859565</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1348607</v>
+        <v>1353446</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>15466807</v>
+        <v>15485261</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3482146</v>
+        <v>3481837</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>40051119</v>
+        <v>40083036</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>22613407</v>
+        <v>22516251</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>259296077</v>
+        <v>259349182</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>350041</v>
+        <v>2750210</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>3847500</v>
+        <v>31699992</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1119597</v>
+        <v>1115492</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>12316496</v>
+        <v>12316149</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1164934</v>
+        <v>1066544</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>12762516</v>
+        <v>11766560</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>119964</v>
+        <v>119533</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1319979</v>
+        <v>1319040</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>475786</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>5242195</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>898823</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>10314596</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>318260</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>3495461</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>239082</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2622384</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>398942</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>4372289</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1290624</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>14751247</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>212848</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>2333547</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>159494</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1750521</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>265445</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2917700</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>185491</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>2042173</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>132265</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1458327</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>105663</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>1166253</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>79180</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>874350</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>56252068</v>
+        <v>57472761</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>61019013</v>
+        <v>61222474</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>512891</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>5894010</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>132406</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1456209</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>209609</v>
+        <v>210217</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>2310655</v>
+        <v>2308402</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>56042459</v>
+        <v>57775435</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7066781</v>
+        <v>7126213</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>78097259</v>
+        <v>78096383</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>48975678</v>
+        <v>50649222</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>48975678</v>
+        <v>50649222</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>48975678</v>
+        <v>50649222</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>48975678</v>
+        <v>50649222</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>48975678</v>
+        <v>50649222</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
